--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536122_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536122_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>L. GARCIA MUNOZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6617</v>
+        <v>2.6704</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1909</v>
+        <v>2.2382</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4707</v>
+        <v>0.4321</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5905</v>
+        <v>1.3555</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8707</v>
+        <v>2.2352</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2802</v>
+        <v>-0.8797</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2445</v>
+        <v>2.9692</v>
       </c>
       <c r="K18" t="n">
-        <v>0.123</v>
+        <v>1.6977</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1215</v>
+        <v>1.2716</v>
       </c>
       <c r="M18" t="n">
-        <v>0.346</v>
+        <v>-1.6138</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7477</v>
+        <v>0.5375</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4017</v>
+        <v>-2.1513</v>
       </c>
       <c r="P18" t="n">
-        <v>2.1448</v>
+        <v>0.195</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9499</v>
       </c>
       <c r="R18" t="n">
         <v>2.1448</v>
       </c>
       <c r="S18" t="n">
-        <v>0.425</v>
+        <v>-0.1001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0536</v>
+        <v>-0.0012</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4785</v>
+        <v>-0.0989</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.4986</v>
+        <v>1.2201</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.4986</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. GARCIA MUNOZ</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4478</v>
+        <v>1.6617</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0157</v>
+        <v>0.1909</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4321</v>
+        <v>1.4707</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1329</v>
+        <v>0.5905</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6201</v>
+        <v>0.8707</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4873</v>
+        <v>-0.2802</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7467</v>
+        <v>0.2445</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0826</v>
+        <v>0.123</v>
       </c>
       <c r="L19" t="n">
-        <v>0.664</v>
+        <v>0.1215</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6138</v>
+        <v>0.346</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5375</v>
+        <v>0.7477</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1513</v>
+        <v>-0.4017</v>
       </c>
       <c r="P19" t="n">
-        <v>0.195</v>
+        <v>2.1448</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9499</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>2.1448</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1001</v>
+        <v>0.425</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0012</v>
+        <v>-0.0536</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0989</v>
+        <v>0.4785</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2201</v>
+        <v>-1.4986</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2201</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.4986</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. GARCIA MUÑOZ</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2226</v>
+        <v>-0.0448</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2226</v>
+        <v>-2.1782</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2.1335</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2226</v>
+        <v>2.3488</v>
       </c>
       <c r="H20" t="n">
-        <v>0.615</v>
+        <v>5.2489</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6075</v>
+        <v>-2.9001</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2226</v>
+        <v>1.1848</v>
       </c>
       <c r="K20" t="n">
-        <v>0.615</v>
+        <v>3.8258</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6075</v>
+        <v>-2.6411</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.164</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.4231</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.259</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.9248</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.9499</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-0.1986</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.4382</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.2396</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>F. SIERRA GALA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0448</v>
+        <v>-0.9865</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1782</v>
+        <v>-1.0679</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1335</v>
+        <v>0.0814</v>
       </c>
       <c r="G21" t="n">
-        <v>2.3488</v>
+        <v>-2.6574</v>
       </c>
       <c r="H21" t="n">
-        <v>5.2489</v>
+        <v>0.4014</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9001</v>
+        <v>-3.0588</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1848</v>
+        <v>-1.788</v>
       </c>
       <c r="K21" t="n">
-        <v>3.8258</v>
+        <v>-0.4755</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.6411</v>
+        <v>-1.3125</v>
       </c>
       <c r="M21" t="n">
-        <v>1.164</v>
+        <v>-0.8694</v>
       </c>
       <c r="N21" t="n">
-        <v>1.4231</v>
+        <v>0.8769</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.259</v>
+        <v>-1.7463</v>
       </c>
       <c r="P21" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-0.9749</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-2.9248</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.9499</v>
+        <v>1.3649</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1986</v>
+        <v>0.0608</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4382</v>
+        <v>0.1964</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2396</v>
+        <v>-0.1356</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2201</v>
+        <v>1.2201</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.4986</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2201</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. SIERRA GALA</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9865</v>
+        <v>-1.7929</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0679</v>
+        <v>-2.7757</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0814</v>
+        <v>0.9828</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.6574</v>
+        <v>0.5065</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4014</v>
+        <v>2.3258</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.0588</v>
+        <v>-1.8193</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.788</v>
+        <v>2.2548</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4755</v>
+        <v>1.5178</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3125</v>
+        <v>0.737</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8694</v>
+        <v>-1.7483</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8769</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7463</v>
+        <v>-2.5563</v>
       </c>
       <c r="P22" t="n">
-        <v>0.39</v>
+        <v>-5.6546</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9749</v>
+        <v>-7.7994</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3649</v>
+        <v>2.1448</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0608</v>
+        <v>0.3579</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1964</v>
+        <v>0.4346</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1356</v>
+        <v>-0.0767</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2201</v>
+        <v>2.9972</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4986</v>
+        <v>2.3343</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2786</v>
+        <v>0.6629</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>M. SERRANO ALVAREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7929</v>
+        <v>-3.564</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7757</v>
+        <v>-5.5309</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9828</v>
+        <v>1.9669</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5065</v>
+        <v>-2.7592</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3258</v>
+        <v>-1.3497</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8193</v>
+        <v>-1.4095</v>
       </c>
       <c r="J23" t="n">
-        <v>2.2548</v>
+        <v>-3.2396</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5178</v>
+        <v>-1.9595</v>
       </c>
       <c r="L23" t="n">
-        <v>0.737</v>
+        <v>-1.28</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7483</v>
+        <v>0.4804</v>
       </c>
       <c r="N23" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.6099</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.5563</v>
+        <v>-0.1295</v>
       </c>
       <c r="P23" t="n">
-        <v>-5.6546</v>
+        <v>-0.7799</v>
       </c>
       <c r="Q23" t="n">
-        <v>-7.7994</v>
+        <v>-1.9499</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1448</v>
+        <v>1.1699</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3579</v>
+        <v>-0.0249</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4346</v>
+        <v>-0.3415</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0767</v>
+        <v>0.3166</v>
       </c>
       <c r="V23" t="n">
-        <v>2.9972</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.3343</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.6629</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. SERRANO ALVAREZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,152 +2380,69 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.564</v>
+        <v>12.438</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.5309</v>
+        <v>2.154399999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>1.9669</v>
+        <v>10.2835</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.7592</v>
+        <v>9.275099999999998</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.3497</v>
+        <v>18.0723</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4095</v>
+        <v>-8.7973</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.2396</v>
+        <v>14.9177</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.9595</v>
+        <v>9.6218</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.28</v>
+        <v>5.2959</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4804</v>
+        <v>-5.6428</v>
       </c>
       <c r="N24" t="n">
-        <v>0.6099</v>
+        <v>8.4505</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1295</v>
+        <v>-14.0932</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7799</v>
+        <v>1.949899999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9499</v>
+        <v>-19.4987</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1699</v>
+        <v>21.4483</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0249</v>
+        <v>0.4972</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3415</v>
+        <v>-0.7579</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3166</v>
+        <v>1.255</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.7159</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>7.4932</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>play_by_play_2536122_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>12.438</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.154499999999998</v>
-      </c>
-      <c r="F25" t="n">
-        <v>10.2835</v>
-      </c>
-      <c r="G25" t="n">
-        <v>9.275099999999998</v>
-      </c>
-      <c r="H25" t="n">
-        <v>18.0722</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-8.7974</v>
-      </c>
-      <c r="J25" t="n">
-        <v>14.9178</v>
-      </c>
-      <c r="K25" t="n">
-        <v>9.621699999999999</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5.2958</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-5.642799999999998</v>
-      </c>
-      <c r="N25" t="n">
-        <v>8.4505</v>
-      </c>
-      <c r="O25" t="n">
-        <v>-14.0932</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.949900000000001</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-19.4987</v>
-      </c>
-      <c r="R25" t="n">
-        <v>21.4483</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0.4972</v>
-      </c>
-      <c r="T25" t="n">
-        <v>-0.7579000000000001</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.255</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0.7159000000000004</v>
-      </c>
-      <c r="W25" t="n">
-        <v>7.4932</v>
-      </c>
-      <c r="X25" t="n">
         <v>-6.7774</v>
       </c>
-      <c r="Y25" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
